--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_repGlobal.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_repGlobal.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="149">
   <si>
     <t>id</t>
   </si>
@@ -286,10 +286,13 @@
     <t>龙之塔占领区 中心点#范围</t>
   </si>
   <si>
+    <t>1#1&amp;10240001#5000|2#2&amp;10240001#3000|3#3&amp;10240001#2000</t>
+  </si>
+  <si>
     <t>排名区间&amp;奖励道具#数量&amp;奖励道具#数量|排名区间&amp;奖励道具#数量&amp;奖励道具#数量</t>
   </si>
   <si>
-    <t>21500004#1|10240001#10000</t>
+    <t>21500004#1</t>
   </si>
   <si>
     <t>胜利方盟主奖励</t>
@@ -2655,9 +2658,11 @@
       <c r="B39" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="D39" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" s="3">
         <v>16001</v>
@@ -2671,10 +2676,10 @@
         <v>56</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="3">
         <v>16001</v>
@@ -2689,7 +2694,7 @@
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="3">
         <v>16001</v>
@@ -2704,7 +2709,7 @@
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="3">
         <v>16001</v>
@@ -2718,10 +2723,10 @@
         <v>56</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E43" s="4">
         <v>16001</v>
@@ -2735,10 +2740,10 @@
         <v>56</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E44" s="4">
         <v>16001</v>
@@ -2755,7 +2760,7 @@
         <v>300</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" s="3">
         <v>16001</v>
@@ -2769,10 +2774,10 @@
         <v>56</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E46" s="3">
         <v>16001</v>
@@ -2789,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E47" s="3">
         <v>16001</v>
@@ -2806,7 +2811,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E48" s="3">
         <v>16001</v>
@@ -2823,7 +2828,7 @@
         <v>6000</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E49" s="3">
         <v>16001</v>
@@ -2840,7 +2845,7 @@
         <v>60</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50" s="3">
         <v>16001</v>
@@ -2857,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51" s="3">
         <v>16001</v>
@@ -2868,13 +2873,13 @@
         <v>17001001</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2">
         <v>17001</v>
@@ -2885,13 +2890,13 @@
         <v>18001001</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53" s="2">
         <v>18001</v>
@@ -2902,13 +2907,13 @@
         <v>18001002</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="2">
         <v>2</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E54" s="2">
         <v>18001</v>
@@ -2919,13 +2924,13 @@
         <v>18001003</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2">
         <v>18001</v>
@@ -2936,13 +2941,13 @@
         <v>19001001</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2">
         <v>50010011</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E56" s="2">
         <v>19001</v>
@@ -2953,13 +2958,13 @@
         <v>19001002</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2">
         <v>10</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2">
         <v>19001</v>
@@ -2970,13 +2975,13 @@
         <v>19001003</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2">
         <v>19001</v>
@@ -2987,13 +2992,13 @@
         <v>19001004</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="2">
         <v>10</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2">
         <v>19001</v>
@@ -3004,13 +3009,13 @@
         <v>19001005</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E60" s="2">
         <v>19001</v>
@@ -3021,13 +3026,13 @@
         <v>19001006</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E61" s="2">
         <v>19001</v>
@@ -3038,13 +3043,13 @@
         <v>21001001</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E62" s="6">
         <v>21001</v>
@@ -3055,13 +3060,13 @@
         <v>21001002</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C63" s="6">
         <v>2000</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E63" s="6">
         <v>21001</v>
@@ -3072,13 +3077,13 @@
         <v>21001003</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E64" s="6">
         <v>21001</v>
@@ -3089,13 +3094,13 @@
         <v>21001004</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" s="6">
         <v>2000</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E65" s="6">
         <v>21001</v>
@@ -3106,13 +3111,13 @@
         <v>21001005</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C66" s="6">
         <v>21600006</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66" s="6">
         <v>21001</v>
@@ -3123,13 +3128,13 @@
         <v>21001006</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E67" s="6">
         <v>21001</v>
@@ -3140,13 +3145,13 @@
         <v>21001007</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" s="23">
         <v>3</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E68" s="6">
         <v>21001</v>
@@ -3157,13 +3162,13 @@
         <v>21001008</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E69" s="6">
         <v>21001</v>
@@ -3171,19 +3176,19 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C70" s="30">
         <v>10</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" s="23" customFormat="1" spans="1:5">
@@ -3191,13 +3196,13 @@
         <v>27000001</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C71" s="23">
         <v>10</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E71" s="41">
         <v>20001</v>
@@ -3336,7 +3341,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>20</v>
@@ -3880,10 +3885,10 @@
         <v>56</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" s="3">
         <v>16001</v>
@@ -3897,10 +3902,10 @@
         <v>56</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="3">
         <v>16001</v>
@@ -3914,10 +3919,10 @@
         <v>56</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="3">
         <v>16001</v>
@@ -3931,10 +3936,10 @@
         <v>56</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" s="3">
         <v>16001</v>
@@ -3948,10 +3953,10 @@
         <v>56</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E43" s="4">
         <v>16001</v>
@@ -3965,10 +3970,10 @@
         <v>56</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E44" s="4">
         <v>16001</v>
@@ -3985,7 +3990,7 @@
         <v>300</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" s="3">
         <v>16001</v>
@@ -3999,10 +4004,10 @@
         <v>56</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E46" s="3">
         <v>16001</v>
@@ -4019,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E47" s="3">
         <v>16001</v>
@@ -4036,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E48" s="3">
         <v>16001</v>
@@ -4053,7 +4058,7 @@
         <v>6000</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E49" s="3">
         <v>16001</v>
@@ -4070,7 +4075,7 @@
         <v>60</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50" s="3">
         <v>16001</v>
@@ -4087,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51" s="3">
         <v>16001</v>
@@ -4098,13 +4103,13 @@
         <v>17001001</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2">
         <v>17001</v>
@@ -4115,13 +4120,13 @@
         <v>18001001</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53" s="2">
         <v>18001</v>
@@ -4132,13 +4137,13 @@
         <v>18001002</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="2">
         <v>2</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E54" s="2">
         <v>18001</v>
@@ -4149,13 +4154,13 @@
         <v>18001003</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2">
         <v>18001</v>
@@ -4166,13 +4171,13 @@
         <v>19001001</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2">
         <v>50010011</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E56" s="2">
         <v>19001</v>
@@ -4183,13 +4188,13 @@
         <v>19001002</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2">
         <v>10</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2">
         <v>19001</v>
@@ -4200,13 +4205,13 @@
         <v>19001003</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2">
         <v>19001</v>
@@ -4217,13 +4222,13 @@
         <v>19001004</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="2">
         <v>10</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2">
         <v>19001</v>
@@ -4234,13 +4239,13 @@
         <v>19001005</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E60" s="2">
         <v>19001</v>
@@ -4251,13 +4256,13 @@
         <v>19001006</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E61" s="2">
         <v>19001</v>
@@ -4268,13 +4273,13 @@
         <v>21001001</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E62" s="6">
         <v>21001</v>
@@ -4285,13 +4290,13 @@
         <v>21001002</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C63" s="6">
         <v>2000</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E63" s="6">
         <v>21001</v>
@@ -4302,13 +4307,13 @@
         <v>21001003</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E64" s="6">
         <v>21001</v>
@@ -4319,13 +4324,13 @@
         <v>21001004</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" s="6">
         <v>2000</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E65" s="6">
         <v>21001</v>
@@ -4336,13 +4341,13 @@
         <v>21001005</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C66" s="6">
         <v>21600006</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66" s="6">
         <v>21001</v>
@@ -4353,13 +4358,13 @@
         <v>21001006</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E67" s="6">
         <v>21001</v>
@@ -4370,13 +4375,13 @@
         <v>21001007</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" s="23">
         <v>3</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E68" s="6">
         <v>21001</v>
@@ -4387,13 +4392,13 @@
         <v>21001008</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E69" s="6">
         <v>21001</v>
@@ -4441,7 +4446,7 @@
         <v>18</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D72" s="25" t="s">
         <v>20</v>
@@ -4475,7 +4480,7 @@
         <v>15</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D74" s="27" t="s">
         <v>24</v>
@@ -4486,19 +4491,19 @@
     </row>
     <row r="75" s="9" customFormat="1" spans="1:5">
       <c r="A75" s="28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C75" s="30">
         <v>10</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4837,7 +4842,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -4852,7 +4857,7 @@
         <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -4941,7 +4946,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -5624,7 +5629,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
@@ -6456,10 +6461,10 @@
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39">
         <v>16001</v>
@@ -6471,10 +6476,10 @@
         <v>56</v>
       </c>
       <c r="K39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M39">
         <v>16001</v>
@@ -6508,10 +6513,10 @@
         <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40">
         <v>16001</v>
@@ -6523,10 +6528,10 @@
         <v>56</v>
       </c>
       <c r="K40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M40">
         <v>16001</v>
@@ -6560,10 +6565,10 @@
         <v>56</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41">
         <v>16001</v>
@@ -6575,10 +6580,10 @@
         <v>56</v>
       </c>
       <c r="K41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M41">
         <v>16001</v>
@@ -6612,10 +6617,10 @@
         <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42">
         <v>16001</v>
@@ -6627,10 +6632,10 @@
         <v>56</v>
       </c>
       <c r="K42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M42">
         <v>16001</v>
@@ -6664,10 +6669,10 @@
         <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E43">
         <v>16001</v>
@@ -6679,10 +6684,10 @@
         <v>56</v>
       </c>
       <c r="K43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M43">
         <v>16001</v>
@@ -6716,10 +6721,10 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E44">
         <v>16001</v>
@@ -6731,10 +6736,10 @@
         <v>56</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M44">
         <v>16001</v>
@@ -6771,7 +6776,7 @@
         <v>300</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45">
         <v>16001</v>
@@ -6786,7 +6791,7 @@
         <v>300</v>
       </c>
       <c r="L45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M45">
         <v>16001</v>
@@ -6820,10 +6825,10 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E46">
         <v>16001</v>
@@ -6835,10 +6840,10 @@
         <v>56</v>
       </c>
       <c r="K46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M46">
         <v>16001</v>
@@ -6875,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E47">
         <v>16001</v>
@@ -6890,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M47">
         <v>16001</v>
@@ -6927,7 +6932,7 @@
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E48">
         <v>16001</v>
@@ -6942,7 +6947,7 @@
         <v>10</v>
       </c>
       <c r="L48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M48">
         <v>16001</v>
@@ -6979,7 +6984,7 @@
         <v>6000</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E49">
         <v>16001</v>
@@ -6994,7 +6999,7 @@
         <v>6000</v>
       </c>
       <c r="L49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M49">
         <v>16001</v>
@@ -7031,7 +7036,7 @@
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50">
         <v>16001</v>
@@ -7046,7 +7051,7 @@
         <v>60</v>
       </c>
       <c r="L50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M50">
         <v>16001</v>
@@ -7083,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51">
         <v>16001</v>
@@ -7098,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M51">
         <v>16001</v>
@@ -7129,13 +7134,13 @@
         <v>17001001</v>
       </c>
       <c r="J52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M52">
         <v>17001</v>
@@ -7166,13 +7171,13 @@
         <v>18001001</v>
       </c>
       <c r="J53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M53">
         <v>18001</v>
@@ -7203,13 +7208,13 @@
         <v>18001002</v>
       </c>
       <c r="J54" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
       <c r="L54" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M54">
         <v>18001</v>
@@ -7240,13 +7245,13 @@
         <v>18001003</v>
       </c>
       <c r="J55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K55">
         <v>1</v>
       </c>
       <c r="L55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M55">
         <v>18001</v>
@@ -7277,13 +7282,13 @@
         <v>19001001</v>
       </c>
       <c r="J56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K56">
         <v>50010011</v>
       </c>
       <c r="L56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M56">
         <v>19001</v>
@@ -7314,13 +7319,13 @@
         <v>19001002</v>
       </c>
       <c r="J57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K57">
         <v>10</v>
       </c>
       <c r="L57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M57">
         <v>19001</v>
@@ -7351,13 +7356,13 @@
         <v>19001003</v>
       </c>
       <c r="J58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L58" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M58">
         <v>19001</v>
@@ -7388,13 +7393,13 @@
         <v>19001004</v>
       </c>
       <c r="J59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K59">
         <v>10</v>
       </c>
       <c r="L59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M59">
         <v>19001</v>
@@ -7425,13 +7430,13 @@
         <v>19001005</v>
       </c>
       <c r="J60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K60" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M60">
         <v>19001</v>
@@ -7462,13 +7467,13 @@
         <v>19001006</v>
       </c>
       <c r="J61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M61">
         <v>19001</v>
@@ -7499,13 +7504,13 @@
         <v>21001001</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E62">
         <v>21001</v>
@@ -7514,13 +7519,13 @@
         <v>21001001</v>
       </c>
       <c r="J62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K62" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L62" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M62">
         <v>21001</v>
@@ -7551,13 +7556,13 @@
         <v>21001002</v>
       </c>
       <c r="B63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C63">
         <v>2000</v>
       </c>
       <c r="D63" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E63">
         <v>21001</v>
@@ -7566,13 +7571,13 @@
         <v>21001002</v>
       </c>
       <c r="J63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K63">
         <v>2000</v>
       </c>
       <c r="L63" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M63">
         <v>21001</v>
@@ -7603,13 +7608,13 @@
         <v>21001003</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E64">
         <v>21001</v>
@@ -7618,13 +7623,13 @@
         <v>21001003</v>
       </c>
       <c r="J64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M64">
         <v>21001</v>
@@ -7655,13 +7660,13 @@
         <v>21001004</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65">
         <v>2000</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E65">
         <v>21001</v>
@@ -7670,13 +7675,13 @@
         <v>21001004</v>
       </c>
       <c r="J65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K65">
         <v>2000</v>
       </c>
       <c r="L65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M65">
         <v>21001</v>
@@ -7707,13 +7712,13 @@
         <v>21001005</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C66">
         <v>21600006</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66">
         <v>21001</v>
@@ -7722,13 +7727,13 @@
         <v>21001005</v>
       </c>
       <c r="J66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K66">
         <v>21600006</v>
       </c>
       <c r="L66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M66">
         <v>21001</v>
@@ -7759,13 +7764,13 @@
         <v>21001006</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E67">
         <v>21001</v>
@@ -7774,13 +7779,13 @@
         <v>21001006</v>
       </c>
       <c r="J67" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M67">
         <v>21001</v>
@@ -7811,13 +7816,13 @@
         <v>21001007</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E68">
         <v>21001</v>
@@ -7826,13 +7831,13 @@
         <v>21001007</v>
       </c>
       <c r="J68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K68">
         <v>3</v>
       </c>
       <c r="L68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M68">
         <v>21001</v>
@@ -7863,13 +7868,13 @@
         <v>21001008</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E69">
         <v>21001</v>
@@ -7878,13 +7883,13 @@
         <v>21001008</v>
       </c>
       <c r="J69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M69">
         <v>21001</v>
@@ -7912,34 +7917,34 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
       <c r="D70" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" t="s">
+        <v>131</v>
+      </c>
+      <c r="I70" t="s">
+        <v>128</v>
+      </c>
+      <c r="J70" t="s">
         <v>129</v>
-      </c>
-      <c r="E70" t="s">
-        <v>130</v>
-      </c>
-      <c r="I70" t="s">
-        <v>127</v>
-      </c>
-      <c r="J70" t="s">
-        <v>128</v>
       </c>
       <c r="K70">
         <v>10</v>
       </c>
       <c r="L70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P70">
         <f t="shared" si="10"/>
